--- a/apps/api/templates/waybill-esm2.xlsx
+++ b/apps/api/templates/waybill-esm2.xlsx
@@ -1096,7 +1096,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="286">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2235,6 +2235,10 @@
     </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2251,43 +2255,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>56160</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>85320</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28440</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Picture 1" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="271440" y="85320"/>
-          <a:ext cx="423000" cy="520920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>42</xdr:col>
@@ -3435,9 +3402,10 @@
       <c r="CF3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AI4" s="9" t="s">
+      <c r="AC4" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="AI4" s="9"/>
       <c r="AJ4" s="9"/>
       <c r="BU4" s="7" t="s">
         <v>6</v>
@@ -3679,7 +3647,7 @@
       <c r="G9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve">{{vehicle_brand}}</t>
         </is>
@@ -10955,12 +10923,11 @@
     </row>
     <row r="148" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="200">
+  <mergeCells count="199">
     <mergeCell ref="T2:AL3"/>
     <mergeCell ref="BF2:BG3"/>
     <mergeCell ref="BV2:CF2"/>
     <mergeCell ref="BV3:CF3"/>
-    <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="BV4:BX4"/>
     <mergeCell ref="BY4:CB4"/>
     <mergeCell ref="CC4:CF4"/>

--- a/apps/api/templates/waybill-esm2.xlsx
+++ b/apps/api/templates/waybill-esm2.xlsx
@@ -1096,7 +1096,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="287">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2239,6 +2239,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3312,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="true" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" s="1" customFormat="true" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="T2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3338,7 +3342,7 @@
         <v>2</v>
       </c>
       <c r="BG2" s="5"/>
-      <c r="BH2" t="inlineStr">
+      <c r="BH2" s="286" t="inlineStr">
         <is>
           <t xml:space="preserve">{{waybill_date}}</t>
         </is>
@@ -3357,7 +3361,7 @@
       <c r="CE2" s="6"/>
       <c r="CF2" s="6"/>
     </row>
-    <row r="3" s="1" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="1" customFormat="true" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
@@ -3377,7 +3381,7 @@
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
-      <c r="AM3" t="inlineStr">
+      <c r="AM3" s="286" t="inlineStr">
         <is>
           <t xml:space="preserve">№ {{waybill_series}}{{waybill_number}}</t>
         </is>
@@ -3792,7 +3796,7 @@
       <c r="G11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="286" t="inlineStr">
         <is>
           <t xml:space="preserve">{{driver_fio}}</t>
         </is>

--- a/apps/api/templates/waybill-esm2.xlsx
+++ b/apps/api/templates/waybill-esm2.xlsx
@@ -1096,7 +1096,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="291">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2239,6 +2239,22 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -3338,11 +3354,16 @@
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
       <c r="AL2" s="4"/>
+      <c r="AM2" s="288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  № {{waybill_series}}{{waybill_number}}</t>
+        </is>
+      </c>
       <c r="BF2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="BG2" s="5"/>
-      <c r="BH2" s="286" t="inlineStr">
+      <c r="BH2" s="289" t="inlineStr">
         <is>
           <t xml:space="preserve">{{waybill_date}}</t>
         </is>
@@ -3381,11 +3402,6 @@
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
-      <c r="AM3" s="286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">№ {{waybill_series}}{{waybill_number}}</t>
-        </is>
-      </c>
       <c r="BF3" s="5"/>
       <c r="BG3" s="5"/>
       <c r="BU3" s="7" t="s">
@@ -3796,7 +3812,7 @@
       <c r="G11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="286" t="inlineStr">
+      <c r="H11" s="290" t="inlineStr">
         <is>
           <t xml:space="preserve">{{driver_fio}}</t>
         </is>
@@ -3895,8 +3911,12 @@
       <c r="C13" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="47" t="s">
-        <v>28</v>
+      <c r="D13" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наименование и адрес объекта
+{{object_line}}
+Выполняемая работа</t>
+        </is>
       </c>
       <c r="E13" s="47"/>
       <c r="F13" s="47"/>
@@ -4473,11 +4493,7 @@
           <t xml:space="preserve">пн {{day1_date}}</t>
         </is>
       </c>
-      <c r="D19" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day1_object}}</t>
-        </is>
-      </c>
+      <c r="D19" s="80"/>
       <c r="E19" s="81"/>
       <c r="F19" s="82"/>
       <c r="G19" s="82"/>
@@ -4813,11 +4829,7 @@
           <t xml:space="preserve">вт {{day2_date}}</t>
         </is>
       </c>
-      <c r="D23" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day2_object}}</t>
-        </is>
-      </c>
+      <c r="D23" s="121"/>
       <c r="E23" s="82"/>
       <c r="F23" s="82"/>
       <c r="G23" s="82"/>
@@ -5153,11 +5165,7 @@
           <t xml:space="preserve">ср {{day3_date}}</t>
         </is>
       </c>
-      <c r="D27" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day3_object}}</t>
-        </is>
-      </c>
+      <c r="D27" s="121"/>
       <c r="E27" s="82"/>
       <c r="F27" s="82"/>
       <c r="G27" s="82"/>
@@ -5493,11 +5501,7 @@
           <t xml:space="preserve">чт {{day4_date}}</t>
         </is>
       </c>
-      <c r="D31" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day4_object}}</t>
-        </is>
-      </c>
+      <c r="D31" s="121"/>
       <c r="E31" s="82"/>
       <c r="F31" s="82"/>
       <c r="G31" s="82"/>
@@ -5833,11 +5837,7 @@
           <t xml:space="preserve">пт {{day5_date}}</t>
         </is>
       </c>
-      <c r="D35" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day5_object}}</t>
-        </is>
-      </c>
+      <c r="D35" s="121"/>
       <c r="E35" s="82"/>
       <c r="F35" s="82"/>
       <c r="G35" s="82"/>
@@ -6173,11 +6173,7 @@
           <t xml:space="preserve">сб {{day6_date}}</t>
         </is>
       </c>
-      <c r="D39" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day6_object}}</t>
-        </is>
-      </c>
+      <c r="D39" s="121"/>
       <c r="E39" s="82"/>
       <c r="F39" s="82"/>
       <c r="G39" s="82"/>
@@ -6513,11 +6509,7 @@
           <t xml:space="preserve">вс {{day7_date}}</t>
         </is>
       </c>
-      <c r="D43" s="121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{day7_object}}</t>
-        </is>
-      </c>
+      <c r="D43" s="121"/>
       <c r="E43" s="82"/>
       <c r="F43" s="82"/>
       <c r="G43" s="82"/>
@@ -7362,8 +7354,13 @@
       <c r="F102" s="155"/>
       <c r="G102" s="155"/>
       <c r="H102" s="155"/>
-      <c r="I102" s="165" t="s">
-        <v>74</v>
+      <c r="I102" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наименование и адрес объекта 
+{{object_line}}
+Выполняемая работа
+в отработанные часы не включать обеденный перерыв</t>
+        </is>
       </c>
       <c r="J102" s="165"/>
       <c r="K102" s="165"/>
@@ -10718,9 +10715,7 @@
       <c r="CG142" s="89"/>
     </row>
     <row r="143" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AL143" s="278" t="s">
-        <v>99</v>
-      </c>
+      <c r="AL143" s="278"/>
       <c r="AM143" s="278"/>
       <c r="AN143" s="278"/>
       <c r="AO143" s="278"/>
@@ -10751,41 +10746,27 @@
       <c r="AM144" s="278"/>
       <c r="AN144" s="278"/>
       <c r="AO144" s="278"/>
-      <c r="AP144" s="279" t="s">
-        <v>101</v>
-      </c>
+      <c r="AP144" s="279"/>
       <c r="AQ144" s="279"/>
       <c r="AR144" s="279"/>
       <c r="AS144" s="279"/>
-      <c r="AT144" s="279" t="s">
-        <v>102</v>
-      </c>
+      <c r="AT144" s="279"/>
       <c r="AU144" s="279"/>
       <c r="AV144" s="279"/>
-      <c r="AW144" s="279" t="s">
-        <v>103</v>
-      </c>
+      <c r="AW144" s="279"/>
       <c r="AX144" s="279"/>
       <c r="AY144" s="279"/>
-      <c r="AZ144" s="279" t="s">
-        <v>104</v>
-      </c>
+      <c r="AZ144" s="279"/>
       <c r="BA144" s="279"/>
       <c r="BB144" s="279"/>
       <c r="BC144" s="279"/>
-      <c r="BD144" s="279" t="s">
-        <v>105</v>
-      </c>
+      <c r="BD144" s="279"/>
       <c r="BE144" s="279"/>
       <c r="BF144" s="279"/>
-      <c r="BG144" s="279" t="s">
-        <v>106</v>
-      </c>
+      <c r="BG144" s="279"/>
       <c r="BH144" s="279"/>
       <c r="BI144" s="279"/>
-      <c r="BJ144" s="279" t="s">
-        <v>107</v>
-      </c>
+      <c r="BJ144" s="279"/>
       <c r="BK144" s="279"/>
       <c r="BL144" s="279"/>
     </row>
@@ -10815,41 +10796,27 @@
       <c r="AM145" s="278"/>
       <c r="AN145" s="278"/>
       <c r="AO145" s="278"/>
-      <c r="AP145" s="279" t="s">
-        <v>108</v>
-      </c>
+      <c r="AP145" s="279"/>
       <c r="AQ145" s="279"/>
       <c r="AR145" s="279"/>
       <c r="AS145" s="279"/>
-      <c r="AT145" s="279" t="s">
-        <v>109</v>
-      </c>
+      <c r="AT145" s="279"/>
       <c r="AU145" s="279"/>
       <c r="AV145" s="279"/>
-      <c r="AW145" s="279" t="s">
-        <v>110</v>
-      </c>
+      <c r="AW145" s="279"/>
       <c r="AX145" s="279"/>
       <c r="AY145" s="279"/>
-      <c r="AZ145" s="279" t="s">
-        <v>111</v>
-      </c>
+      <c r="AZ145" s="279"/>
       <c r="BA145" s="279"/>
       <c r="BB145" s="279"/>
       <c r="BC145" s="279"/>
-      <c r="BD145" s="279" t="s">
-        <v>112</v>
-      </c>
+      <c r="BD145" s="279"/>
       <c r="BE145" s="279"/>
       <c r="BF145" s="279"/>
-      <c r="BG145" s="279" t="s">
-        <v>113</v>
-      </c>
+      <c r="BG145" s="279"/>
       <c r="BH145" s="279"/>
       <c r="BI145" s="279"/>
-      <c r="BJ145" s="280" t="s">
-        <v>114</v>
-      </c>
+      <c r="BJ145" s="280"/>
       <c r="BK145" s="281"/>
       <c r="BL145" s="281"/>
     </row>
@@ -10858,36 +10825,24 @@
       <c r="AM146" s="278"/>
       <c r="AN146" s="278"/>
       <c r="AO146" s="278"/>
-      <c r="AP146" s="282" t="s">
-        <v>115</v>
-      </c>
+      <c r="AP146" s="282"/>
       <c r="AQ146" s="282"/>
       <c r="AR146" s="282"/>
       <c r="AS146" s="282"/>
-      <c r="AT146" s="282" t="s">
-        <v>116</v>
-      </c>
+      <c r="AT146" s="282"/>
       <c r="AU146" s="282"/>
       <c r="AV146" s="282"/>
-      <c r="AW146" s="279" t="s">
-        <v>117</v>
-      </c>
+      <c r="AW146" s="279"/>
       <c r="AX146" s="279"/>
       <c r="AY146" s="279"/>
-      <c r="AZ146" s="279" t="s">
-        <v>116</v>
-      </c>
+      <c r="AZ146" s="279"/>
       <c r="BA146" s="279"/>
       <c r="BB146" s="279"/>
       <c r="BC146" s="279"/>
-      <c r="BD146" s="279" t="s">
-        <v>118</v>
-      </c>
+      <c r="BD146" s="279"/>
       <c r="BE146" s="279"/>
       <c r="BF146" s="279"/>
-      <c r="BG146" s="279" t="s">
-        <v>119</v>
-      </c>
+      <c r="BG146" s="279"/>
       <c r="BH146" s="279"/>
       <c r="BI146" s="279"/>
     </row>
@@ -10927,7 +10882,7 @@
     </row>
     <row r="148" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="199">
+  <mergeCells count="201">
     <mergeCell ref="T2:AL3"/>
     <mergeCell ref="BF2:BG3"/>
     <mergeCell ref="BV2:CF2"/>
@@ -11127,6 +11082,8 @@
     <mergeCell ref="BD146:BF146"/>
     <mergeCell ref="BG146:BI146"/>
     <mergeCell ref="U147:X147"/>
+    <mergeCell ref="AM2:BE3"/>
+    <mergeCell ref="BH2:BO3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0" footer="0"/>
